--- a/02_加值成品/九下/九下4-3_三種難度測驗卷.xlsx
+++ b/02_加值成品/九下/九下4-3_三種難度測驗卷.xlsx
@@ -490,19 +490,23 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:H12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="62" customWidth="1" min="2" max="2"/>
+    <col width="54" customWidth="1" min="2" max="2"/>
     <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="42" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="40" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>國三下學期 九下4-3 永續經營　測驗　★☆☆ 基礎（記憶・理解）</t>
+          <t>國三下學期 九下4-3 永續經營　測驗　★☆☆ 基礎（記憶・理解）（四選一單選）</t>
         </is>
       </c>
     </row>
@@ -519,16 +523,36 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
+          <t>(A)</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>(B)</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>(C)</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>(D)</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
           <t>答案</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="H2" s="2" t="inlineStr">
         <is>
           <t>解析</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="34" customHeight="1">
+    <row r="3" ht="40" customHeight="1">
       <c r="A3" s="3" t="n">
         <v>1</v>
       </c>
@@ -537,18 +561,38 @@
           <t>滿足當代又不損後代的發展是？</t>
         </is>
       </c>
-      <c r="C3" s="5" t="inlineStr">
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>社會</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
         <is>
           <t>永續發展</t>
         </is>
       </c>
-      <c r="D3" s="4" t="inlineStr">
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>世代公平</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>損及後代資源</t>
+        </is>
+      </c>
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
         <is>
           <t>永續</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="34" customHeight="1">
+    <row r="4" ht="40" customHeight="1">
       <c r="A4" s="6" t="n">
         <v>2</v>
       </c>
@@ -557,18 +601,38 @@
           <t>永續要兼顧環境經濟與？</t>
         </is>
       </c>
-      <c r="C4" s="8" t="inlineStr">
+      <c r="C4" s="7" t="inlineStr">
         <is>
           <t>社會</t>
         </is>
       </c>
       <c r="D4" s="7" t="inlineStr">
         <is>
+          <t>減量</t>
+        </is>
+      </c>
+      <c r="E4" s="7" t="inlineStr">
+        <is>
+          <t>減少排碳</t>
+        </is>
+      </c>
+      <c r="F4" s="7" t="inlineStr">
+        <is>
+          <t>經濟</t>
+        </is>
+      </c>
+      <c r="G4" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H4" s="7" t="inlineStr">
+        <is>
           <t>三面向</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="34" customHeight="1">
+    <row r="5" ht="40" customHeight="1">
       <c r="A5" s="3" t="n">
         <v>3</v>
       </c>
@@ -577,18 +641,38 @@
           <t>把廢棄物再利用是？</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr">
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>減少塑膠</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>減少排碳</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>減量/減塑</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
         <is>
           <t>資源回收</t>
         </is>
       </c>
-      <c r="D5" s="4" t="inlineStr">
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
         <is>
           <t>循環</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="34" customHeight="1">
+    <row r="6" ht="40" customHeight="1">
       <c r="A6" s="6" t="n">
         <v>4</v>
       </c>
@@ -597,18 +681,38 @@
           <t>取代化石燃料的是？</t>
         </is>
       </c>
-      <c r="C6" s="8" t="inlineStr">
+      <c r="C6" s="7" t="inlineStr">
+        <is>
+          <t>減量/減塑</t>
+        </is>
+      </c>
+      <c r="D6" s="7" t="inlineStr">
         <is>
           <t>再生能源</t>
         </is>
       </c>
-      <c r="D6" s="7" t="inlineStr">
+      <c r="E6" s="7" t="inlineStr">
+        <is>
+          <t>永續發展</t>
+        </is>
+      </c>
+      <c r="F6" s="7" t="inlineStr">
+        <is>
+          <t>世代公平</t>
+        </is>
+      </c>
+      <c r="G6" s="8" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H6" s="7" t="inlineStr">
         <is>
           <t>綠能</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="34" customHeight="1">
+    <row r="7" ht="40" customHeight="1">
       <c r="A7" s="3" t="n">
         <v>5</v>
       </c>
@@ -617,18 +721,38 @@
           <t>減少使用一次性用品是？</t>
         </is>
       </c>
-      <c r="C7" s="5" t="inlineStr">
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>減量/減塑</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>減少排碳</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>資源回收</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
         <is>
           <t>減量</t>
         </is>
       </c>
-      <c r="D7" s="4" t="inlineStr">
+      <c r="G7" s="5" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
         <is>
           <t>減廢</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="34" customHeight="1">
+    <row r="8" ht="40" customHeight="1">
       <c r="A8" s="6" t="n">
         <v>6</v>
       </c>
@@ -637,18 +761,38 @@
           <t>保護多種生物是保護？</t>
         </is>
       </c>
-      <c r="C8" s="8" t="inlineStr">
+      <c r="C8" s="7" t="inlineStr">
+        <is>
+          <t>資源回收</t>
+        </is>
+      </c>
+      <c r="D8" s="7" t="inlineStr">
+        <is>
+          <t>社會</t>
+        </is>
+      </c>
+      <c r="E8" s="7" t="inlineStr">
+        <is>
+          <t>永續發展</t>
+        </is>
+      </c>
+      <c r="F8" s="7" t="inlineStr">
         <is>
           <t>生物多樣性</t>
         </is>
       </c>
-      <c r="D8" s="7" t="inlineStr">
+      <c r="G8" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H8" s="7" t="inlineStr">
         <is>
           <t>生態</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="34" customHeight="1">
+    <row r="9" ht="40" customHeight="1">
       <c r="A9" s="3" t="n">
         <v>7</v>
       </c>
@@ -657,18 +801,38 @@
           <t>自備購物袋是為了？</t>
         </is>
       </c>
-      <c r="C9" s="5" t="inlineStr">
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>減量/減塑</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>經濟</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
         <is>
           <t>減少塑膠</t>
         </is>
       </c>
-      <c r="D9" s="4" t="inlineStr">
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>世代公平</t>
+        </is>
+      </c>
+      <c r="G9" s="5" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
         <is>
           <t>減廢</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="34" customHeight="1">
+    <row r="10" ht="40" customHeight="1">
       <c r="A10" s="6" t="n">
         <v>8</v>
       </c>
@@ -677,18 +841,38 @@
           <t>永續發展強調哪種公平？</t>
         </is>
       </c>
-      <c r="C10" s="8" t="inlineStr">
+      <c r="C10" s="7" t="inlineStr">
+        <is>
+          <t>經濟</t>
+        </is>
+      </c>
+      <c r="D10" s="7" t="inlineStr">
+        <is>
+          <t>環境經濟社會</t>
+        </is>
+      </c>
+      <c r="E10" s="7" t="inlineStr">
+        <is>
+          <t>減量</t>
+        </is>
+      </c>
+      <c r="F10" s="7" t="inlineStr">
         <is>
           <t>世代公平</t>
         </is>
       </c>
-      <c r="D10" s="7" t="inlineStr">
+      <c r="G10" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H10" s="7" t="inlineStr">
         <is>
           <t>公平</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="34" customHeight="1">
+    <row r="11" ht="40" customHeight="1">
       <c r="A11" s="3" t="n">
         <v>9</v>
       </c>
@@ -697,18 +881,38 @@
           <t>資源回收是為了讓資源？</t>
         </is>
       </c>
-      <c r="C11" s="5" t="inlineStr">
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>減少排碳</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>環境經濟社會</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
         <is>
           <t>再利用</t>
         </is>
       </c>
-      <c r="D11" s="4" t="inlineStr">
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>資源永續</t>
+        </is>
+      </c>
+      <c r="G11" s="5" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H11" s="4" t="inlineStr">
         <is>
           <t>循環</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="34" customHeight="1">
+    <row r="12" ht="40" customHeight="1">
       <c r="A12" s="6" t="n">
         <v>10</v>
       </c>
@@ -717,12 +921,32 @@
           <t>永續發展要兼顧環境、社會與？</t>
         </is>
       </c>
-      <c r="C12" s="8" t="inlineStr">
+      <c r="C12" s="7" t="inlineStr">
         <is>
           <t>經濟</t>
         </is>
       </c>
       <c r="D12" s="7" t="inlineStr">
+        <is>
+          <t>再利用</t>
+        </is>
+      </c>
+      <c r="E12" s="7" t="inlineStr">
+        <is>
+          <t>減少塑膠</t>
+        </is>
+      </c>
+      <c r="F12" s="7" t="inlineStr">
+        <is>
+          <t>再生能源</t>
+        </is>
+      </c>
+      <c r="G12" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H12" s="7" t="inlineStr">
         <is>
           <t>三面向</t>
         </is>
@@ -730,7 +954,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A1:H1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -742,19 +966,23 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:H12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="62" customWidth="1" min="2" max="2"/>
+    <col width="54" customWidth="1" min="2" max="2"/>
     <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="42" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="40" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>國三下學期 九下4-3 永續經營　測驗　★★☆ 進階（應用・分析）</t>
+          <t>國三下學期 九下4-3 永續經營　測驗　★★☆ 進階（應用・分析）（四選一單選）</t>
         </is>
       </c>
     </row>
@@ -771,16 +999,36 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
+          <t>(A)</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>(B)</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>(C)</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>(D)</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
           <t>答案</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="H2" s="2" t="inlineStr">
         <is>
           <t>解析</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="34" customHeight="1">
+    <row r="3" ht="40" customHeight="1">
       <c r="A3" s="3" t="n">
         <v>1</v>
       </c>
@@ -789,18 +1037,38 @@
           <t>永續發展的三大面向？</t>
         </is>
       </c>
-      <c r="C3" s="5" t="inlineStr">
+      <c r="C3" s="4" t="inlineStr">
         <is>
           <t>環境經濟社會</t>
         </is>
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
+          <t>永續發展</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>每個人</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>再生能源</t>
+        </is>
+      </c>
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
+        <is>
           <t>三者</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="34" customHeight="1">
+    <row r="4" ht="40" customHeight="1">
       <c r="A4" s="6" t="n">
         <v>2</v>
       </c>
@@ -809,18 +1077,38 @@
           <t>資源回收屬於永續的哪環？</t>
         </is>
       </c>
-      <c r="C4" s="8" t="inlineStr">
+      <c r="C4" s="7" t="inlineStr">
         <is>
           <t>資源永續</t>
         </is>
       </c>
       <c r="D4" s="7" t="inlineStr">
         <is>
+          <t>永續發展</t>
+        </is>
+      </c>
+      <c r="E4" s="7" t="inlineStr">
+        <is>
+          <t>社會</t>
+        </is>
+      </c>
+      <c r="F4" s="7" t="inlineStr">
+        <is>
+          <t>再生能源</t>
+        </is>
+      </c>
+      <c r="G4" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H4" s="7" t="inlineStr">
+        <is>
           <t>循環</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="34" customHeight="1">
+    <row r="5" ht="40" customHeight="1">
       <c r="A5" s="3" t="n">
         <v>3</v>
       </c>
@@ -829,18 +1117,38 @@
           <t>綠色消費指？</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr">
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>節能減廢回收綠色消費</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
         <is>
           <t>選環境友善產品</t>
         </is>
       </c>
-      <c r="D5" s="4" t="inlineStr">
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>生態服務下降糧食醫藥受損</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>資源耗竭損及後代與生態</t>
+        </is>
+      </c>
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
         <is>
           <t>消費</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="34" customHeight="1">
+    <row r="6" ht="40" customHeight="1">
       <c r="A6" s="6" t="n">
         <v>4</v>
       </c>
@@ -849,18 +1157,38 @@
           <t>保育生物多樣性的意義？</t>
         </is>
       </c>
-      <c r="C6" s="8" t="inlineStr">
+      <c r="C6" s="7" t="inlineStr">
+        <is>
+          <t>世代公平</t>
+        </is>
+      </c>
+      <c r="D6" s="7" t="inlineStr">
+        <is>
+          <t>環境經濟社會</t>
+        </is>
+      </c>
+      <c r="E6" s="7" t="inlineStr">
         <is>
           <t>維持生態平衡</t>
         </is>
       </c>
-      <c r="D6" s="7" t="inlineStr">
+      <c r="F6" s="7" t="inlineStr">
+        <is>
+          <t>生物多樣性</t>
+        </is>
+      </c>
+      <c r="G6" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H6" s="7" t="inlineStr">
         <is>
           <t>生態</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="34" customHeight="1">
+    <row r="7" ht="40" customHeight="1">
       <c r="A7" s="3" t="n">
         <v>5</v>
       </c>
@@ -869,18 +1197,38 @@
           <t>搭大眾運輸有助永續因為？</t>
         </is>
       </c>
-      <c r="C7" s="5" t="inlineStr">
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>永續發展</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>環境經濟社會</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>資源回收</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
         <is>
           <t>減少排碳</t>
         </is>
       </c>
-      <c r="D7" s="4" t="inlineStr">
+      <c r="G7" s="5" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
         <is>
           <t>減排</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="34" customHeight="1">
+    <row r="8" ht="40" customHeight="1">
       <c r="A8" s="6" t="n">
         <v>6</v>
       </c>
@@ -889,18 +1237,38 @@
           <t>永續是誰的責任？</t>
         </is>
       </c>
-      <c r="C8" s="8" t="inlineStr">
+      <c r="C8" s="7" t="inlineStr">
+        <is>
+          <t>經濟</t>
+        </is>
+      </c>
+      <c r="D8" s="7" t="inlineStr">
+        <is>
+          <t>減少排碳</t>
+        </is>
+      </c>
+      <c r="E8" s="7" t="inlineStr">
         <is>
           <t>每個人</t>
         </is>
       </c>
-      <c r="D8" s="7" t="inlineStr">
+      <c r="F8" s="7" t="inlineStr">
+        <is>
+          <t>資源永續</t>
+        </is>
+      </c>
+      <c r="G8" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H8" s="7" t="inlineStr">
         <is>
           <t>共責</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="34" customHeight="1">
+    <row r="9" ht="40" customHeight="1">
       <c r="A9" s="3" t="n">
         <v>7</v>
       </c>
@@ -909,18 +1277,38 @@
           <t>過度開發違反永續因為？</t>
         </is>
       </c>
-      <c r="C9" s="5" t="inlineStr">
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>減量</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
         <is>
           <t>損及後代資源</t>
         </is>
       </c>
-      <c r="D9" s="4" t="inlineStr">
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>減少塑膠</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>再利用</t>
+        </is>
+      </c>
+      <c r="G9" s="5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
         <is>
           <t>耗竭</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="34" customHeight="1">
+    <row r="10" ht="40" customHeight="1">
       <c r="A10" s="6" t="n">
         <v>8</v>
       </c>
@@ -929,18 +1317,38 @@
           <t>再生能源為何較永續？</t>
         </is>
       </c>
-      <c r="C10" s="8" t="inlineStr">
+      <c r="C10" s="7" t="inlineStr">
+        <is>
+          <t>永續發展</t>
+        </is>
+      </c>
+      <c r="D10" s="7" t="inlineStr">
         <is>
           <t>可再生少污染</t>
         </is>
       </c>
-      <c r="D10" s="7" t="inlineStr">
+      <c r="E10" s="7" t="inlineStr">
+        <is>
+          <t>維持生態平衡</t>
+        </is>
+      </c>
+      <c r="F10" s="7" t="inlineStr">
+        <is>
+          <t>環境經濟社會</t>
+        </is>
+      </c>
+      <c r="G10" s="8" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H10" s="7" t="inlineStr">
         <is>
           <t>永續</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="34" customHeight="1">
+    <row r="11" ht="40" customHeight="1">
       <c r="A11" s="3" t="n">
         <v>9</v>
       </c>
@@ -949,18 +1357,38 @@
           <t>永續發展除環境、經濟外還需兼顧？</t>
         </is>
       </c>
-      <c r="C11" s="5" t="inlineStr">
+      <c r="C11" s="4" t="inlineStr">
         <is>
           <t>社會</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
+          <t>資源永續</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>減量</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>減少排碳</t>
+        </is>
+      </c>
+      <c r="G11" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H11" s="4" t="inlineStr">
+        <is>
           <t>社會</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="34" customHeight="1">
+    <row r="12" ht="40" customHeight="1">
       <c r="A12" s="6" t="n">
         <v>10</v>
       </c>
@@ -969,12 +1397,32 @@
           <t>自備環保杯袋屬於哪種行動？</t>
         </is>
       </c>
-      <c r="C12" s="8" t="inlineStr">
+      <c r="C12" s="7" t="inlineStr">
         <is>
           <t>減量/減塑</t>
         </is>
       </c>
       <c r="D12" s="7" t="inlineStr">
+        <is>
+          <t>維持生態平衡</t>
+        </is>
+      </c>
+      <c r="E12" s="7" t="inlineStr">
+        <is>
+          <t>社會</t>
+        </is>
+      </c>
+      <c r="F12" s="7" t="inlineStr">
+        <is>
+          <t>資源回收</t>
+        </is>
+      </c>
+      <c r="G12" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H12" s="7" t="inlineStr">
         <is>
           <t>減廢</t>
         </is>
@@ -982,7 +1430,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A1:H1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -994,19 +1442,23 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:H12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="62" customWidth="1" min="2" max="2"/>
+    <col width="54" customWidth="1" min="2" max="2"/>
     <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="42" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="40" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>國三下學期 九下4-3 永續經營　測驗　★★★ 挑戰（評鑑・創造）</t>
+          <t>國三下學期 九下4-3 永續經營　測驗　★★★ 挑戰（評鑑・創造）（四選一單選）</t>
         </is>
       </c>
     </row>
@@ -1023,16 +1475,36 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
+          <t>(A)</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>(B)</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>(C)</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>(D)</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
           <t>答案</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="H2" s="2" t="inlineStr">
         <is>
           <t>解析</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="34" customHeight="1">
+    <row r="3" ht="40" customHeight="1">
       <c r="A3" s="3" t="n">
         <v>1</v>
       </c>
@@ -1041,18 +1513,38 @@
           <t>為何永續發展要兼顧三面向？</t>
         </is>
       </c>
-      <c r="C3" s="5" t="inlineStr">
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>減緩調適皆屬永續實踐</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>節能回收綠化環境教育</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
         <is>
           <t>僅顧單一面向難以長久平衡發展</t>
         </is>
       </c>
-      <c r="D3" s="4" t="inlineStr">
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>綠能產業兼顧經濟與環境</t>
+        </is>
+      </c>
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
         <is>
           <t>平衡</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="34" customHeight="1">
+    <row r="4" ht="40" customHeight="1">
       <c r="A4" s="6" t="n">
         <v>2</v>
       </c>
@@ -1061,18 +1553,38 @@
           <t>舉例說明發展與環保如何並存？</t>
         </is>
       </c>
-      <c r="C4" s="8" t="inlineStr">
+      <c r="C4" s="7" t="inlineStr">
+        <is>
+          <t>生態服務下降糧食醫藥受損</t>
+        </is>
+      </c>
+      <c r="D4" s="7" t="inlineStr">
         <is>
           <t>綠能產業兼顧經濟與環境</t>
         </is>
       </c>
-      <c r="D4" s="7" t="inlineStr">
+      <c r="E4" s="7" t="inlineStr">
+        <is>
+          <t>當代不應耗盡後代所需資源</t>
+        </is>
+      </c>
+      <c r="F4" s="7" t="inlineStr">
+        <is>
+          <t>資源耗竭損及後代與生態</t>
+        </is>
+      </c>
+      <c r="G4" s="8" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H4" s="7" t="inlineStr">
         <is>
           <t>雙贏</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="34" customHeight="1">
+    <row r="5" ht="40" customHeight="1">
       <c r="A5" s="3" t="n">
         <v>3</v>
       </c>
@@ -1081,18 +1593,38 @@
           <t>分析過度捕撈為何不永續？</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr">
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>選環境友善產品</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>生態服務下降糧食醫藥受損</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>減緩調適皆屬永續實踐</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
         <is>
           <t>資源耗竭損及後代與生態</t>
         </is>
       </c>
-      <c r="D5" s="4" t="inlineStr">
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
         <is>
           <t>耗竭</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="34" customHeight="1">
+    <row r="6" ht="40" customHeight="1">
       <c r="A6" s="6" t="n">
         <v>4</v>
       </c>
@@ -1101,18 +1633,38 @@
           <t>個人可如何實踐永續生活(至少三項)？</t>
         </is>
       </c>
-      <c r="C6" s="8" t="inlineStr">
+      <c r="C6" s="7" t="inlineStr">
+        <is>
+          <t>綠能產業兼顧經濟與環境</t>
+        </is>
+      </c>
+      <c r="D6" s="7" t="inlineStr">
         <is>
           <t>節能減廢回收綠色消費</t>
         </is>
       </c>
-      <c r="D6" s="7" t="inlineStr">
+      <c r="E6" s="7" t="inlineStr">
+        <is>
+          <t>生態服務下降糧食醫藥受損</t>
+        </is>
+      </c>
+      <c r="F6" s="7" t="inlineStr">
+        <is>
+          <t>節能、回收、綠色消費</t>
+        </is>
+      </c>
+      <c r="G6" s="8" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H6" s="7" t="inlineStr">
         <is>
           <t>行動</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="34" customHeight="1">
+    <row r="7" ht="40" customHeight="1">
       <c r="A7" s="3" t="n">
         <v>5</v>
       </c>
@@ -1121,18 +1673,38 @@
           <t>生物多樣性喪失對人類的影響？</t>
         </is>
       </c>
-      <c r="C7" s="5" t="inlineStr">
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>綠能產業兼顧經濟與環境</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
         <is>
           <t>生態服務下降糧食醫藥受損</t>
         </is>
       </c>
-      <c r="D7" s="4" t="inlineStr">
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>節能、回收、綠色消費</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>減緩調適皆屬永續實踐</t>
+        </is>
+      </c>
+      <c r="G7" s="5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
         <is>
           <t>衝擊</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="34" customHeight="1">
+    <row r="8" ht="40" customHeight="1">
       <c r="A8" s="6" t="n">
         <v>6</v>
       </c>
@@ -1141,18 +1713,38 @@
           <t>永續發展與氣候變遷對策關係？</t>
         </is>
       </c>
-      <c r="C8" s="8" t="inlineStr">
+      <c r="C8" s="7" t="inlineStr">
         <is>
           <t>減緩調適皆屬永續實踐</t>
         </is>
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
+          <t>節能減廢回收綠色消費</t>
+        </is>
+      </c>
+      <c r="E8" s="7" t="inlineStr">
+        <is>
+          <t>節能、回收、綠色消費</t>
+        </is>
+      </c>
+      <c r="F8" s="7" t="inlineStr">
+        <is>
+          <t>僅顧單一面向難以長久平衡發展</t>
+        </is>
+      </c>
+      <c r="G8" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H8" s="7" t="inlineStr">
+        <is>
           <t>關聯</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="34" customHeight="1">
+    <row r="9" ht="40" customHeight="1">
       <c r="A9" s="3" t="n">
         <v>7</v>
       </c>
@@ -1161,18 +1753,38 @@
           <t>為何說永續是世代之間的公平？</t>
         </is>
       </c>
-      <c r="C9" s="5" t="inlineStr">
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>節能減廢回收綠色消費</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>綠能產業兼顧經濟與環境</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
         <is>
           <t>當代不應耗盡後代所需資源</t>
         </is>
       </c>
-      <c r="D9" s="4" t="inlineStr">
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>節能回收綠化環境教育</t>
+        </is>
+      </c>
+      <c r="G9" s="5" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
         <is>
           <t>公平</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="34" customHeight="1">
+    <row r="10" ht="40" customHeight="1">
       <c r="A10" s="6" t="n">
         <v>8</v>
       </c>
@@ -1181,18 +1793,38 @@
           <t>規劃校園永續可從哪些面向著手？</t>
         </is>
       </c>
-      <c r="C10" s="8" t="inlineStr">
+      <c r="C10" s="7" t="inlineStr">
+        <is>
+          <t>選環境友善產品</t>
+        </is>
+      </c>
+      <c r="D10" s="7" t="inlineStr">
+        <is>
+          <t>綠能產業兼顧經濟與環境</t>
+        </is>
+      </c>
+      <c r="E10" s="7" t="inlineStr">
         <is>
           <t>節能回收綠化環境教育</t>
         </is>
       </c>
-      <c r="D10" s="7" t="inlineStr">
+      <c r="F10" s="7" t="inlineStr">
+        <is>
+          <t>資源耗竭損及後代與生態</t>
+        </is>
+      </c>
+      <c r="G10" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H10" s="7" t="inlineStr">
         <is>
           <t>方案</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="34" customHeight="1">
+    <row r="11" ht="40" customHeight="1">
       <c r="A11" s="3" t="n">
         <v>9</v>
       </c>
@@ -1201,18 +1833,38 @@
           <t>為何過度捕撈不符合永續？</t>
         </is>
       </c>
-      <c r="C11" s="5" t="inlineStr">
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>選環境友善產品</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>節能、回收、綠色消費</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>綠能產業兼顧經濟與環境</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="inlineStr">
         <is>
           <t>資源耗竭損及後代與生態</t>
         </is>
       </c>
-      <c r="D11" s="4" t="inlineStr">
+      <c r="G11" s="5" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H11" s="4" t="inlineStr">
         <is>
           <t>耗竭</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="34" customHeight="1">
+    <row r="12" ht="40" customHeight="1">
       <c r="A12" s="6" t="n">
         <v>10</v>
       </c>
@@ -1221,12 +1873,32 @@
           <t>個人實踐永續的做法舉三項？</t>
         </is>
       </c>
-      <c r="C12" s="8" t="inlineStr">
+      <c r="C12" s="7" t="inlineStr">
         <is>
           <t>節能、回收、綠色消費</t>
         </is>
       </c>
       <c r="D12" s="7" t="inlineStr">
+        <is>
+          <t>資源耗竭損及後代與生態</t>
+        </is>
+      </c>
+      <c r="E12" s="7" t="inlineStr">
+        <is>
+          <t>僅顧單一面向難以長久平衡發展</t>
+        </is>
+      </c>
+      <c r="F12" s="7" t="inlineStr">
+        <is>
+          <t>選環境友善產品</t>
+        </is>
+      </c>
+      <c r="G12" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H12" s="7" t="inlineStr">
         <is>
           <t>行動</t>
         </is>
@@ -1234,7 +1906,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A1:H1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/02_加值成品/九下/九下4-3_三種難度測驗卷.xlsx
+++ b/02_加值成品/九下/九下4-3_三種難度測驗卷.xlsx
@@ -588,7 +588,7 @@
       </c>
       <c r="H3" s="4" t="inlineStr">
         <is>
-          <t>永續</t>
+          <t>永續：既滿足現在人的生活需求，又不會讓後代子孫失去資源可用的發展方式，稱為永續發展</t>
         </is>
       </c>
     </row>
@@ -628,7 +628,7 @@
       </c>
       <c r="H4" s="7" t="inlineStr">
         <is>
-          <t>三面向</t>
+          <t>三面向：永續發展不能只顧一項，必須同時兼顧環境保護、經濟發展和社會公平</t>
         </is>
       </c>
     </row>
@@ -668,7 +668,7 @@
       </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
-          <t>循環</t>
+          <t>循環：將原本要丟棄的物品重新處理再利用，就是資源回收，能讓資源循環使用</t>
         </is>
       </c>
     </row>
@@ -708,7 +708,7 @@
       </c>
       <c r="H6" s="7" t="inlineStr">
         <is>
-          <t>綠能</t>
+          <t>綠能：太陽能、風力等可以不斷再生的能源，能用來取代會用盡的化石燃料</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
-          <t>減廢</t>
+          <t>減廢：少用只用一次就丟的物品，能從源頭減少垃圾產生的數量</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="H8" s="7" t="inlineStr">
         <is>
-          <t>生態</t>
+          <t>生態：保護地球上各式各樣的生物物種，就是在維護生物多樣性與生態平衡</t>
         </is>
       </c>
     </row>
@@ -828,7 +828,7 @@
       </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
-          <t>減廢</t>
+          <t>減廢：自己攜帶購物袋，可以減少使用免洗塑膠袋，降低垃圾與污染</t>
         </is>
       </c>
     </row>
@@ -868,7 +868,7 @@
       </c>
       <c r="H10" s="7" t="inlineStr">
         <is>
-          <t>公平</t>
+          <t>公平：永續發展強調這一代人使用資源時，也要為下一代留下足夠的資源，這叫世代公平</t>
         </is>
       </c>
     </row>
@@ -908,7 +908,7 @@
       </c>
       <c r="H11" s="4" t="inlineStr">
         <is>
-          <t>循環</t>
+          <t>循環：把使用過的物品回收處理後再製成新產品,讓有限的資源可以重複循環利用</t>
         </is>
       </c>
     </row>
@@ -948,7 +948,7 @@
       </c>
       <c r="H12" s="7" t="inlineStr">
         <is>
-          <t>三面向</t>
+          <t>三面向：永續發展強調同時兼顧環境保護、社會公平與經濟發展這三個面向,不能只顧其中一項</t>
         </is>
       </c>
     </row>
@@ -1064,7 +1064,7 @@
       </c>
       <c r="H3" s="4" t="inlineStr">
         <is>
-          <t>三者</t>
+          <t>三者：永續發展要同時兼顧環境保護、經濟成長與社會公平這三個面向，缺一不可</t>
         </is>
       </c>
     </row>
@@ -1104,7 +1104,7 @@
       </c>
       <c r="H4" s="7" t="inlineStr">
         <is>
-          <t>循環</t>
+          <t>循環：把廢棄物回收再利用，是讓有限資源能不斷循環使用，屬於資源永續的一環</t>
         </is>
       </c>
     </row>
@@ -1119,24 +1119,24 @@
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
+          <t>綠能產業兼顧經濟與環境</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>選環境友善產品</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>當代不應耗盡後代所需資源</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
           <t>節能減廢回收綠色消費</t>
         </is>
       </c>
-      <c r="D5" s="4" t="inlineStr">
-        <is>
-          <t>選環境友善產品</t>
-        </is>
-      </c>
-      <c r="E5" s="4" t="inlineStr">
-        <is>
-          <t>生態服務下降糧食醫藥受損</t>
-        </is>
-      </c>
-      <c r="F5" s="4" t="inlineStr">
-        <is>
-          <t>資源耗竭損及後代與生態</t>
-        </is>
-      </c>
       <c r="G5" s="5" t="inlineStr">
         <is>
           <t>B</t>
@@ -1144,7 +1144,7 @@
       </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
-          <t>消費</t>
+          <t>消費：購買生產過程對環境傷害較小、對生態友善的產品，就是綠色消費</t>
         </is>
       </c>
     </row>
@@ -1184,7 +1184,7 @@
       </c>
       <c r="H6" s="7" t="inlineStr">
         <is>
-          <t>生態</t>
+          <t>生態：保護多種多樣的生物物種，能維持生態系統原本的平衡與穩定運作</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
-          <t>減排</t>
+          <t>減排：多人共乘公車、捷運等大眾運輸，能減少私人交通工具排放的二氧化碳</t>
         </is>
       </c>
     </row>
@@ -1264,7 +1264,7 @@
       </c>
       <c r="H8" s="7" t="inlineStr">
         <is>
-          <t>共責</t>
+          <t>共責：永續發展不只是政府或企業的事，每一個人在生活中都能盡一份力</t>
         </is>
       </c>
     </row>
@@ -1304,7 +1304,7 @@
       </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
-          <t>耗竭</t>
+          <t>耗竭：過度開發會把資源用得太快太多，使後代子孫可用的資源變得不足</t>
         </is>
       </c>
     </row>
@@ -1344,7 +1344,7 @@
       </c>
       <c r="H10" s="7" t="inlineStr">
         <is>
-          <t>永續</t>
+          <t>永續：太陽能、風力等再生能源用之不竭又較少造成污染，比化石燃料更符合永續精神</t>
         </is>
       </c>
     </row>
@@ -1384,7 +1384,7 @@
       </c>
       <c r="H11" s="4" t="inlineStr">
         <is>
-          <t>社會</t>
+          <t>社會：除了環境保護和經濟發展,永續發展也要考慮社會公平與人們的生活福祉，三者缺一不可</t>
         </is>
       </c>
     </row>
@@ -1424,7 +1424,7 @@
       </c>
       <c r="H12" s="7" t="inlineStr">
         <is>
-          <t>減廢</t>
+          <t>減廢：自己攜帶環保杯袋，可以減少一次性用品的使用量，屬於源頭減量、減少廢棄物的行動</t>
         </is>
       </c>
     </row>
@@ -1515,12 +1515,12 @@
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
-          <t>減緩調適皆屬永續實踐</t>
+          <t>節能減廢回收綠色消費</t>
         </is>
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
-          <t>節能回收綠化環境教育</t>
+          <t>資源耗竭損及後代與生態</t>
         </is>
       </c>
       <c r="E3" s="4" t="inlineStr">
@@ -1530,7 +1530,7 @@
       </c>
       <c r="F3" s="4" t="inlineStr">
         <is>
-          <t>綠能產業兼顧經濟與環境</t>
+          <t>當代不應耗盡後代所需資源</t>
         </is>
       </c>
       <c r="G3" s="5" t="inlineStr">
@@ -1540,7 +1540,7 @@
       </c>
       <c r="H3" s="4" t="inlineStr">
         <is>
-          <t>平衡</t>
+          <t>平衡：如果只重視經濟卻忽略環境，或只重視環境卻犧牲民生，都難以長久維持，必須三者兼顧才能平衡發展</t>
         </is>
       </c>
     </row>
@@ -1555,7 +1555,7 @@
       </c>
       <c r="C4" s="7" t="inlineStr">
         <is>
-          <t>生態服務下降糧食醫藥受損</t>
+          <t>資源耗竭損及後代與生態</t>
         </is>
       </c>
       <c r="D4" s="7" t="inlineStr">
@@ -1565,12 +1565,12 @@
       </c>
       <c r="E4" s="7" t="inlineStr">
         <is>
-          <t>當代不應耗盡後代所需資源</t>
+          <t>僅顧單一面向難以長久平衡發展</t>
         </is>
       </c>
       <c r="F4" s="7" t="inlineStr">
         <is>
-          <t>資源耗竭損及後代與生態</t>
+          <t>節能減廢回收綠色消費</t>
         </is>
       </c>
       <c r="G4" s="8" t="inlineStr">
@@ -1580,7 +1580,7 @@
       </c>
       <c r="H4" s="7" t="inlineStr">
         <is>
-          <t>雙贏</t>
+          <t>雙贏：發展太陽能、風力等綠色能源產業，既能創造工作機會帶動經濟，又能減少污染保護環境，是雙贏的做法</t>
         </is>
       </c>
     </row>
@@ -1595,19 +1595,19 @@
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>選環境友善產品</t>
+          <t>僅顧單一面向難以長久平衡發展</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
+          <t>減緩調適皆屬永續實踐</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
           <t>生態服務下降糧食醫藥受損</t>
         </is>
       </c>
-      <c r="E5" s="4" t="inlineStr">
-        <is>
-          <t>減緩調適皆屬永續實踐</t>
-        </is>
-      </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
           <t>資源耗竭損及後代與生態</t>
@@ -1620,7 +1620,7 @@
       </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
-          <t>耗竭</t>
+          <t>耗竭：捕撈速度超過魚群繁殖的速度，會使魚類資源逐漸枯竭，不僅影響後代可用的漁獲，也破壞海洋生態</t>
         </is>
       </c>
     </row>
@@ -1635,7 +1635,7 @@
       </c>
       <c r="C6" s="7" t="inlineStr">
         <is>
-          <t>綠能產業兼顧經濟與環境</t>
+          <t>節能回收綠化環境教育</t>
         </is>
       </c>
       <c r="D6" s="7" t="inlineStr">
@@ -1645,12 +1645,12 @@
       </c>
       <c r="E6" s="7" t="inlineStr">
         <is>
-          <t>生態服務下降糧食醫藥受損</t>
+          <t>僅顧單一面向難以長久平衡發展</t>
         </is>
       </c>
       <c r="F6" s="7" t="inlineStr">
         <is>
-          <t>節能、回收、綠色消費</t>
+          <t>資源耗竭損及後代與生態</t>
         </is>
       </c>
       <c r="G6" s="8" t="inlineStr">
@@ -1660,7 +1660,7 @@
       </c>
       <c r="H6" s="7" t="inlineStr">
         <is>
-          <t>行動</t>
+          <t>行動：日常生活中可以做到節約能源、減少製造垃圾、確實做好資源回收，並選擇對環境友善的綠色消費</t>
         </is>
       </c>
     </row>
@@ -1685,12 +1685,12 @@
       </c>
       <c r="E7" s="4" t="inlineStr">
         <is>
-          <t>節能、回收、綠色消費</t>
+          <t>減緩調適皆屬永續實踐</t>
         </is>
       </c>
       <c r="F7" s="4" t="inlineStr">
         <is>
-          <t>減緩調適皆屬永續實踐</t>
+          <t>資源耗竭損及後代與生態</t>
         </is>
       </c>
       <c r="G7" s="5" t="inlineStr">
@@ -1700,7 +1700,7 @@
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
-          <t>衝擊</t>
+          <t>衝擊：物種大量消失會使自然界提供的授粉、淨化水質等生態服務跟著減弱，也可能影響糧食生產與新藥物的研發來源</t>
         </is>
       </c>
     </row>
@@ -1720,17 +1720,17 @@
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
+          <t>綠能產業兼顧經濟與環境</t>
+        </is>
+      </c>
+      <c r="E8" s="7" t="inlineStr">
+        <is>
           <t>節能減廢回收綠色消費</t>
         </is>
       </c>
-      <c r="E8" s="7" t="inlineStr">
-        <is>
-          <t>節能、回收、綠色消費</t>
-        </is>
-      </c>
       <c r="F8" s="7" t="inlineStr">
         <is>
-          <t>僅顧單一面向難以長久平衡發展</t>
+          <t>選環境友善產品</t>
         </is>
       </c>
       <c r="G8" s="8" t="inlineStr">
@@ -1740,7 +1740,7 @@
       </c>
       <c r="H8" s="7" t="inlineStr">
         <is>
-          <t>關聯</t>
+          <t>關聯：不管是減少溫室氣體排放的減緩，還是調整生活因應變化的調適，都是在為環境、經濟與社會的長久平衡努力，屬於永續發展的具體實踐</t>
         </is>
       </c>
     </row>
@@ -1755,12 +1755,12 @@
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>節能減廢回收綠色消費</t>
+          <t>僅顧單一面向難以長久平衡發展</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>綠能產業兼顧經濟與環境</t>
+          <t>資源耗竭損及後代與生態</t>
         </is>
       </c>
       <c r="E9" s="4" t="inlineStr">
@@ -1780,7 +1780,7 @@
       </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
-          <t>公平</t>
+          <t>公平：這一代人如果把資源用光、把環境破壞殆盡，下一代就沒有足夠資源可用，因此永續發展重視當代與後代之間的公平</t>
         </is>
       </c>
     </row>
@@ -1795,12 +1795,12 @@
       </c>
       <c r="C10" s="7" t="inlineStr">
         <is>
-          <t>選環境友善產品</t>
+          <t>綠能產業兼顧經濟與環境</t>
         </is>
       </c>
       <c r="D10" s="7" t="inlineStr">
         <is>
-          <t>綠能產業兼顧經濟與環境</t>
+          <t>僅顧單一面向難以長久平衡發展</t>
         </is>
       </c>
       <c r="E10" s="7" t="inlineStr">
@@ -1820,7 +1820,7 @@
       </c>
       <c r="H10" s="7" t="inlineStr">
         <is>
-          <t>方案</t>
+          <t>方案：校園可以從節約能源、落實資源回收、增加綠化植栽，以及推動環境教育等多個面向一起著手，打造永續校園</t>
         </is>
       </c>
     </row>
@@ -1830,24 +1830,24 @@
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>為何過度捕撈不符合永續？</t>
+          <t>為何過度捕撈不符合永續發展的精神？</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
+          <t>當代不應耗盡後代所需資源</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>僅顧單一面向難以長久平衡發展</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
           <t>選環境友善產品</t>
         </is>
       </c>
-      <c r="D11" s="4" t="inlineStr">
-        <is>
-          <t>節能、回收、綠色消費</t>
-        </is>
-      </c>
-      <c r="E11" s="4" t="inlineStr">
-        <is>
-          <t>綠能產業兼顧經濟與環境</t>
-        </is>
-      </c>
       <c r="F11" s="4" t="inlineStr">
         <is>
           <t>資源耗竭損及後代與生態</t>
@@ -1860,7 +1860,7 @@
       </c>
       <c r="H11" s="4" t="inlineStr">
         <is>
-          <t>耗竭</t>
+          <t>耗竭：過度捕撈會讓魚類數量來不及繁殖恢復，長期下來資源枯竭，不但破壞生態平衡，也讓後代子孫沒有資源可用，違反永續發展的精神</t>
         </is>
       </c>
     </row>
@@ -1870,37 +1870,37 @@
       </c>
       <c r="B12" s="7" t="inlineStr">
         <is>
-          <t>個人實踐永續的做法舉三項？</t>
+          <t>請舉三項個人可以實踐永續生活的做法？</t>
         </is>
       </c>
       <c r="C12" s="7" t="inlineStr">
         <is>
-          <t>節能、回收、綠色消費</t>
+          <t>當代不應耗盡後代所需資源</t>
         </is>
       </c>
       <c r="D12" s="7" t="inlineStr">
         <is>
-          <t>資源耗竭損及後代與生態</t>
+          <t>選環境友善產品</t>
         </is>
       </c>
       <c r="E12" s="7" t="inlineStr">
         <is>
-          <t>僅顧單一面向難以長久平衡發展</t>
+          <t>節能減廢回收綠色消費</t>
         </is>
       </c>
       <c r="F12" s="7" t="inlineStr">
         <is>
-          <t>選環境友善產品</t>
+          <t>生態服務下降糧食醫藥受損</t>
         </is>
       </c>
       <c r="G12" s="8" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="H12" s="7" t="inlineStr">
         <is>
-          <t>行動</t>
+          <t>行動：個人可以從隨手節約能源、減少廢棄物產生、確實做好資源回收、選購對環境友善的綠色消費商品等日常小事做起，一起實踐永續生活</t>
         </is>
       </c>
     </row>

--- a/02_加值成品/九下/九下4-3_三種難度測驗卷.xlsx
+++ b/02_加值成品/九下/九下4-3_三種難度測驗卷.xlsx
@@ -608,17 +608,17 @@
       </c>
       <c r="D4" s="7" t="inlineStr">
         <is>
-          <t>減量</t>
+          <t>每個人</t>
         </is>
       </c>
       <c r="E4" s="7" t="inlineStr">
         <is>
-          <t>減少排碳</t>
+          <t>世代公平</t>
         </is>
       </c>
       <c r="F4" s="7" t="inlineStr">
         <is>
-          <t>經濟</t>
+          <t>永續發展</t>
         </is>
       </c>
       <c r="G4" s="8" t="inlineStr">
@@ -723,7 +723,7 @@
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>減量/減塑</t>
+          <t>環境經濟社會</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
@@ -733,7 +733,7 @@
       </c>
       <c r="E7" s="4" t="inlineStr">
         <is>
-          <t>資源回收</t>
+          <t>社會</t>
         </is>
       </c>
       <c r="F7" s="4" t="inlineStr">
@@ -928,17 +928,17 @@
       </c>
       <c r="D12" s="7" t="inlineStr">
         <is>
+          <t>可再生少污染</t>
+        </is>
+      </c>
+      <c r="E12" s="7" t="inlineStr">
+        <is>
+          <t>再生能源</t>
+        </is>
+      </c>
+      <c r="F12" s="7" t="inlineStr">
+        <is>
           <t>再利用</t>
-        </is>
-      </c>
-      <c r="E12" s="7" t="inlineStr">
-        <is>
-          <t>減少塑膠</t>
-        </is>
-      </c>
-      <c r="F12" s="7" t="inlineStr">
-        <is>
-          <t>再生能源</t>
         </is>
       </c>
       <c r="G12" s="8" t="inlineStr">
@@ -1044,17 +1044,17 @@
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
-          <t>永續發展</t>
+          <t>減少排碳</t>
         </is>
       </c>
       <c r="E3" s="4" t="inlineStr">
         <is>
-          <t>每個人</t>
+          <t>資源回收</t>
         </is>
       </c>
       <c r="F3" s="4" t="inlineStr">
         <is>
-          <t>再生能源</t>
+          <t>減量</t>
         </is>
       </c>
       <c r="G3" s="5" t="inlineStr">
@@ -1369,12 +1369,12 @@
       </c>
       <c r="E11" s="4" t="inlineStr">
         <is>
-          <t>減量</t>
+          <t>再生能源</t>
         </is>
       </c>
       <c r="F11" s="4" t="inlineStr">
         <is>
-          <t>減少排碳</t>
+          <t>永續發展</t>
         </is>
       </c>
       <c r="G11" s="5" t="inlineStr">
@@ -1404,17 +1404,17 @@
       </c>
       <c r="D12" s="7" t="inlineStr">
         <is>
-          <t>維持生態平衡</t>
+          <t>生物多樣性</t>
         </is>
       </c>
       <c r="E12" s="7" t="inlineStr">
         <is>
-          <t>社會</t>
+          <t>減少塑膠</t>
         </is>
       </c>
       <c r="F12" s="7" t="inlineStr">
         <is>
-          <t>資源回收</t>
+          <t>永續發展</t>
         </is>
       </c>
       <c r="G12" s="8" t="inlineStr">
